--- a/data/item.xlsx
+++ b/data/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doc\SoftE\item\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9157F28-B51D-475B-8368-9A8A96403147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE6E298-FF97-49F2-B676-9C071EF2E662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.4">
@@ -457,13 +457,6 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.4"/>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.4"/>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.4"/>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.4"/>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/item.xlsx
+++ b/data/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doc\SoftE\item\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE6E298-FF97-49F2-B676-9C071EF2E662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403ED3D8-B80D-4E85-8D7D-8E5972DB56BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/item.xlsx
+++ b/data/item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doc\SoftE\item\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403ED3D8-B80D-4E85-8D7D-8E5972DB56BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E87563-CC1E-4097-8252-DFD0E893C6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="276">
   <si>
     <t>名称</t>
   </si>
@@ -44,6 +44,811 @@
   </si>
   <si>
     <t>修改人</t>
+  </si>
+  <si>
+    <t>S8050</t>
+  </si>
+  <si>
+    <t>SOT-23</t>
+  </si>
+  <si>
+    <t>C20099125</t>
+  </si>
+  <si>
+    <t>三极管</t>
+  </si>
+  <si>
+    <t>默认</t>
+  </si>
+  <si>
+    <t>2026-08-03 15:55:47</t>
+  </si>
+  <si>
+    <t>CJ2301</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>场效应管</t>
+  </si>
+  <si>
+    <t>2026-08-03 15:57:18</t>
+  </si>
+  <si>
+    <t>B5819W</t>
+  </si>
+  <si>
+    <t>SOT-123</t>
+  </si>
+  <si>
+    <t>肖特基二极管</t>
+  </si>
+  <si>
+    <t>2026-08-03 15:59:42</t>
+  </si>
+  <si>
+    <t>IPEX-1</t>
+  </si>
+  <si>
+    <t>SMD</t>
+  </si>
+  <si>
+    <t>RF射频同轴连接器</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:01:36</t>
+  </si>
+  <si>
+    <t>CH224A</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:02:48</t>
+  </si>
+  <si>
+    <t>NCE3035Q</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:04:03</t>
+  </si>
+  <si>
+    <t>2N7002</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:04:38</t>
+  </si>
+  <si>
+    <t>PSMN1R8-40YLC</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:06:46</t>
+  </si>
+  <si>
+    <t>SW6306V</t>
+  </si>
+  <si>
+    <t>QFN-60</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:09:24</t>
+  </si>
+  <si>
+    <t>LM393</t>
+  </si>
+  <si>
+    <t>SOP-8</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:09:58</t>
+  </si>
+  <si>
+    <t>CJ3400</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:10:49</t>
+  </si>
+  <si>
+    <t>AO3415</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:12:17</t>
+  </si>
+  <si>
+    <t>CJAC80SN10</t>
+  </si>
+  <si>
+    <t>PDFNWB5x6-8L</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:13:56</t>
+  </si>
+  <si>
+    <t>LM358</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:14:25</t>
+  </si>
+  <si>
+    <t>TL431</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:14:56</t>
+  </si>
+  <si>
+    <t>16N03</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:15:17</t>
+  </si>
+  <si>
+    <t>CSD18540Q5B</t>
+  </si>
+  <si>
+    <t>VSON-8</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:16:40</t>
+  </si>
+  <si>
+    <t>HYG015N04LS1C2</t>
+  </si>
+  <si>
+    <t>PDFN5x6-8L</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:18:03</t>
+  </si>
+  <si>
+    <t>IP5306</t>
+  </si>
+  <si>
+    <t>ESOP-8</t>
+  </si>
+  <si>
+    <t>C181692</t>
+  </si>
+  <si>
+    <t>电池管理</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:20:59</t>
+  </si>
+  <si>
+    <t>LR8341A-T33</t>
+  </si>
+  <si>
+    <t>SOT-23-3L</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:22:15</t>
+  </si>
+  <si>
+    <t>SX1308</t>
+  </si>
+  <si>
+    <t>SOT-23-6</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:23:27</t>
+  </si>
+  <si>
+    <t>ME6118A33PG</t>
+  </si>
+  <si>
+    <t>SOT-89-3</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:24:33</t>
+  </si>
+  <si>
+    <t>AMS1117-3.3</t>
+  </si>
+  <si>
+    <t>SOT-223</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:27:07</t>
+  </si>
+  <si>
+    <t>SOT-89</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:27:48</t>
+  </si>
+  <si>
+    <t>CJ78L05</t>
+  </si>
+  <si>
+    <t>SOT-89-3L</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:28:51</t>
+  </si>
+  <si>
+    <t>TPS630701RNMR</t>
+  </si>
+  <si>
+    <t>VQFN-15-HR(2.5x3)</t>
+  </si>
+  <si>
+    <t>C2876599</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:30:35</t>
+  </si>
+  <si>
+    <t>MP2315GJ-Z</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:32:11</t>
+  </si>
+  <si>
+    <t>MC34063ADR</t>
+  </si>
+  <si>
+    <t>C100023</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:35:44</t>
+  </si>
+  <si>
+    <t>TP4056</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:37:26</t>
+  </si>
+  <si>
+    <t>AMS1117-1.8</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:38:24</t>
+  </si>
+  <si>
+    <t>AMS1117-5.0</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:40:31</t>
+  </si>
+  <si>
+    <t>SCT2450STER</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:41:39</t>
+  </si>
+  <si>
+    <t>MP2482DN-LF-Z</t>
+  </si>
+  <si>
+    <t>SOIC-8-EP</t>
+  </si>
+  <si>
+    <t>C56736</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:42:49</t>
+  </si>
+  <si>
+    <t>XB8089D</t>
+  </si>
+  <si>
+    <t>C79928</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:43:57</t>
+  </si>
+  <si>
+    <t>AMS1117-2.5</t>
+  </si>
+  <si>
+    <t>SOT223</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:44:31</t>
+  </si>
+  <si>
+    <t>MP1495SGJ-Z</t>
+  </si>
+  <si>
+    <t>TSOT-23-8</t>
+  </si>
+  <si>
+    <t>C371525</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:46:16</t>
+  </si>
+  <si>
+    <t>LM5145RGYR</t>
+  </si>
+  <si>
+    <t>VQFN-20-EP(3.5x4.5)</t>
+  </si>
+  <si>
+    <t>C485912</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:47:51</t>
+  </si>
+  <si>
+    <t>TPS54540DDAR</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:49:31</t>
+  </si>
+  <si>
+    <t>TPS5430DDAR</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:50:23</t>
+  </si>
+  <si>
+    <t>DRV8701ERGER</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:51:09</t>
+  </si>
+  <si>
+    <t>EG2125</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:51:45</t>
+  </si>
+  <si>
+    <t>EG2134</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:52:05</t>
+  </si>
+  <si>
+    <t>EG2104</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:52:49</t>
+  </si>
+  <si>
+    <t>IR2104STRPBF</t>
+  </si>
+  <si>
+    <t>SOIC-8</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:54:05</t>
+  </si>
+  <si>
+    <t>EG2181</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:54:26</t>
+  </si>
+  <si>
+    <t>UCC27211DR</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:55:17</t>
+  </si>
+  <si>
+    <t>TB6612FNG</t>
+  </si>
+  <si>
+    <t>SSOP-24</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:56:25</t>
+  </si>
+  <si>
+    <t>ETA6002E8A</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:57:26</t>
+  </si>
+  <si>
+    <t>74HC245PW,118</t>
+  </si>
+  <si>
+    <t>TSSOP-20</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:58:32</t>
+  </si>
+  <si>
+    <t>74HC125PW,118</t>
+  </si>
+  <si>
+    <t>TSSOP-14</t>
+  </si>
+  <si>
+    <t>2026-08-03 16:59:37</t>
+  </si>
+  <si>
+    <t>LM5069MM-2/NOPB</t>
+  </si>
+  <si>
+    <t>VSSOP-10</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:01:02</t>
+  </si>
+  <si>
+    <t>L9110S</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:02:14</t>
+  </si>
+  <si>
+    <t>74HC126D,653</t>
+  </si>
+  <si>
+    <t>SOIC-14</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:03:03</t>
+  </si>
+  <si>
+    <t>PCM1770PW</t>
+  </si>
+  <si>
+    <t>TSSOP-16</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:04:02</t>
+  </si>
+  <si>
+    <t>PCF8563T/5,518</t>
+  </si>
+  <si>
+    <t>SO-8</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:05:01</t>
+  </si>
+  <si>
+    <t>TJA1044GTK/3Z</t>
+  </si>
+  <si>
+    <t>HVSON-8-EP(3x3)</t>
+  </si>
+  <si>
+    <t>C2157795</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:06:16</t>
+  </si>
+  <si>
+    <t>OPA2350UA/2K5</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:07:10</t>
+  </si>
+  <si>
+    <t>LMV358IDR</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:07:57</t>
+  </si>
+  <si>
+    <t>INA226AIDGSR</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:11:46</t>
+  </si>
+  <si>
+    <t>INA240A1PWR</t>
+  </si>
+  <si>
+    <t>TSSOP-8</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:12:38</t>
+  </si>
+  <si>
+    <t>SS12</t>
+  </si>
+  <si>
+    <t>SMA</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:13:34</t>
+  </si>
+  <si>
+    <t>SS14</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:15:54</t>
+  </si>
+  <si>
+    <t>US1M</t>
+  </si>
+  <si>
+    <t>C7420317</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:15:24</t>
+  </si>
+  <si>
+    <t>1N4001</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:17:16</t>
+  </si>
+  <si>
+    <t>MBR0540</t>
+  </si>
+  <si>
+    <t>SOD-123</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:18:02</t>
+  </si>
+  <si>
+    <t>SS36B</t>
+  </si>
+  <si>
+    <t>SMB</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:18:46</t>
+  </si>
+  <si>
+    <t>SS510</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:19:20</t>
+  </si>
+  <si>
+    <t>B340A</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:19:47</t>
+  </si>
+  <si>
+    <t>BAT54W</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:20:54</t>
+  </si>
+  <si>
+    <t>SMBJ16CA</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:21:23</t>
+  </si>
+  <si>
+    <t>BAT54C</t>
+  </si>
+  <si>
+    <t>SO5-23</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:21:51</t>
+  </si>
+  <si>
+    <t>MURS140T3G</t>
+  </si>
+  <si>
+    <t>C21243</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:23:16</t>
+  </si>
+  <si>
+    <t>SS24</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:23:34</t>
+  </si>
+  <si>
+    <t>FR107</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:24:14</t>
+  </si>
+  <si>
+    <t>SS54</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:24:32</t>
+  </si>
+  <si>
+    <t>SMF</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:24:59</t>
+  </si>
+  <si>
+    <t>DSK310</t>
+  </si>
+  <si>
+    <t>SOD-123FL</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:25:41</t>
+  </si>
+  <si>
+    <t>NUP2105</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:26:45</t>
+  </si>
+  <si>
+    <t>SMBJ24A</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:27:07</t>
+  </si>
+  <si>
+    <t>BZT52C3V6</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:29:47</t>
+  </si>
+  <si>
+    <t>BZT52C3V3</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:30:35</t>
+  </si>
+  <si>
+    <t>SMBJ30CA</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:31:00</t>
+  </si>
+  <si>
+    <t>SMDJ30CA</t>
+  </si>
+  <si>
+    <t>SMC</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:31:45</t>
+  </si>
+  <si>
+    <t>BZT52C4V3</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:32:16</t>
+  </si>
+  <si>
+    <t>BZT52C16</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:32:59</t>
+  </si>
+  <si>
+    <t>SMBJ12A</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:33:21</t>
+  </si>
+  <si>
+    <t>SMBJ12CA</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:33:50</t>
+  </si>
+  <si>
+    <t>SMFJ26CA</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:34:41</t>
+  </si>
+  <si>
+    <t>BZT52C15</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:35:12</t>
+  </si>
+  <si>
+    <t>SMAJ12A</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:36:05</t>
+  </si>
+  <si>
+    <t>ZMM5V1</t>
+  </si>
+  <si>
+    <t>LL-34</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:36:48</t>
+  </si>
+  <si>
+    <t>BZT52C12</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:37:29</t>
+  </si>
+  <si>
+    <t>SMAJ36A</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:38:20</t>
+  </si>
+  <si>
+    <t>W25Q64JVSSIQ</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:39:46</t>
+  </si>
+  <si>
+    <t>X322516MLB4SI</t>
+  </si>
+  <si>
+    <t>SMD3225-4P</t>
+  </si>
+  <si>
+    <t>C13738</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:40:53</t>
+  </si>
+  <si>
+    <t>X50328MSB2GI</t>
+  </si>
+  <si>
+    <t>SMD5032-2P</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:41:52</t>
+  </si>
+  <si>
+    <t>XL7EL89CKI-111YLC-24M</t>
+  </si>
+  <si>
+    <t>SMD2016-4P</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:43:28</t>
+  </si>
+  <si>
+    <t>XL2MI-111-24M</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:45:19</t>
+  </si>
+  <si>
+    <t>X1E0000210202</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:46:26</t>
+  </si>
+  <si>
+    <t>CSTNE8M00G520000R0</t>
+  </si>
+  <si>
+    <t>SMD3213-3P</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:48:19</t>
+  </si>
+  <si>
+    <t>STC32F12K54-64I-LQFP48</t>
+  </si>
+  <si>
+    <t>LQFP-48(7x7)</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:49:13</t>
+  </si>
+  <si>
+    <t>CH340C</t>
+  </si>
+  <si>
+    <t>SOP-16</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:50:09</t>
+  </si>
+  <si>
+    <t>X503212MSB2GI</t>
+  </si>
+  <si>
+    <t>2026-08-03 17:53:15</t>
+  </si>
+  <si>
+    <t>谢忠宝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -427,10 +1232,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:H104"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -456,12 +1261,2689 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <v>6</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" t="s">
+        <v>69</v>
+      </c>
+      <c r="H22" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24">
+        <v>25</v>
+      </c>
+      <c r="D24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25">
+        <v>16</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26">
+        <v>20</v>
+      </c>
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H26" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27">
+        <v>6</v>
+      </c>
+      <c r="D27" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" t="s">
+        <v>84</v>
+      </c>
+      <c r="H27" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A28" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" t="s">
+        <v>86</v>
+      </c>
+      <c r="H28" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A29" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H29" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A30" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" t="s">
+        <v>91</v>
+      </c>
+      <c r="H30" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A31" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31">
+        <v>30</v>
+      </c>
+      <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" t="s">
+        <v>93</v>
+      </c>
+      <c r="H31" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32">
+        <v>6</v>
+      </c>
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" t="s">
+        <v>95</v>
+      </c>
+      <c r="H32" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A33" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" t="s">
+        <v>97</v>
+      </c>
+      <c r="H33" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A34" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34">
+        <v>9</v>
+      </c>
+      <c r="D34" t="s">
+        <v>100</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" t="s">
+        <v>101</v>
+      </c>
+      <c r="H34" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A35" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+      <c r="D35" t="s">
+        <v>103</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" t="s">
+        <v>104</v>
+      </c>
+      <c r="H35" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A36" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36">
+        <v>3</v>
+      </c>
+      <c r="D36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" t="s">
+        <v>107</v>
+      </c>
+      <c r="H36" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A37" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37">
+        <v>7</v>
+      </c>
+      <c r="D37" t="s">
+        <v>110</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" t="s">
+        <v>111</v>
+      </c>
+      <c r="H37" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A38" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+      <c r="D38" t="s">
+        <v>114</v>
+      </c>
+      <c r="E38" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" t="s">
+        <v>115</v>
+      </c>
+      <c r="H38" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A39" t="s">
+        <v>116</v>
+      </c>
+      <c r="B39" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" t="s">
+        <v>117</v>
+      </c>
+      <c r="H39" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A40" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40">
+        <v>4</v>
+      </c>
+      <c r="D40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" t="s">
+        <v>119</v>
+      </c>
+      <c r="H40" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A41" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H41" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A42" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" t="s">
+        <v>123</v>
+      </c>
+      <c r="H42" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A43" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" t="s">
+        <v>125</v>
+      </c>
+      <c r="H43" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A44" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44">
+        <v>8</v>
+      </c>
+      <c r="D44" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" t="s">
+        <v>127</v>
+      </c>
+      <c r="H44" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A45" t="s">
+        <v>128</v>
+      </c>
+      <c r="B45" t="s">
+        <v>129</v>
+      </c>
+      <c r="C45">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" t="s">
+        <v>130</v>
+      </c>
+      <c r="H45" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A46" t="s">
+        <v>131</v>
+      </c>
+      <c r="B46" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46">
+        <v>6</v>
+      </c>
+      <c r="D46" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" t="s">
+        <v>132</v>
+      </c>
+      <c r="H46" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A47" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" t="s">
+        <v>129</v>
+      </c>
+      <c r="C47">
+        <v>10</v>
+      </c>
+      <c r="D47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" t="s">
+        <v>134</v>
+      </c>
+      <c r="H47" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A48" t="s">
+        <v>135</v>
+      </c>
+      <c r="B48" t="s">
+        <v>136</v>
+      </c>
+      <c r="C48">
+        <v>3</v>
+      </c>
+      <c r="D48" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" t="s">
+        <v>137</v>
+      </c>
+      <c r="H48" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A49" t="s">
+        <v>138</v>
+      </c>
+      <c r="B49" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="D49" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" t="s">
+        <v>139</v>
+      </c>
+      <c r="H49" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A50" t="s">
+        <v>140</v>
+      </c>
+      <c r="B50" t="s">
+        <v>141</v>
+      </c>
+      <c r="C50">
+        <v>5</v>
+      </c>
+      <c r="D50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" t="s">
+        <v>142</v>
+      </c>
+      <c r="H50" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A51" t="s">
+        <v>143</v>
+      </c>
+      <c r="B51" t="s">
+        <v>144</v>
+      </c>
+      <c r="C51">
+        <v>9</v>
+      </c>
+      <c r="D51" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" t="s">
+        <v>145</v>
+      </c>
+      <c r="H51" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A52" t="s">
+        <v>146</v>
+      </c>
+      <c r="B52" t="s">
+        <v>147</v>
+      </c>
+      <c r="C52">
+        <v>2</v>
+      </c>
+      <c r="D52" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52" t="s">
+        <v>148</v>
+      </c>
+      <c r="H52" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A53" t="s">
+        <v>149</v>
+      </c>
+      <c r="B53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53">
+        <v>7</v>
+      </c>
+      <c r="D53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" t="s">
+        <v>12</v>
+      </c>
+      <c r="G53" t="s">
+        <v>150</v>
+      </c>
+      <c r="H53" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A54" t="s">
+        <v>151</v>
+      </c>
+      <c r="B54" t="s">
+        <v>152</v>
+      </c>
+      <c r="C54">
+        <v>4</v>
+      </c>
+      <c r="D54" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54" t="s">
+        <v>153</v>
+      </c>
+      <c r="H54" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A55" t="s">
+        <v>154</v>
+      </c>
+      <c r="B55" t="s">
+        <v>155</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+      <c r="D55" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" t="s">
+        <v>12</v>
+      </c>
+      <c r="G55" t="s">
+        <v>156</v>
+      </c>
+      <c r="H55" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A56" t="s">
+        <v>157</v>
+      </c>
+      <c r="B56" t="s">
+        <v>158</v>
+      </c>
+      <c r="C56">
+        <v>20</v>
+      </c>
+      <c r="D56" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" t="s">
+        <v>12</v>
+      </c>
+      <c r="G56" t="s">
+        <v>159</v>
+      </c>
+      <c r="H56" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A57" t="s">
+        <v>160</v>
+      </c>
+      <c r="B57" t="s">
+        <v>161</v>
+      </c>
+      <c r="C57">
+        <v>10</v>
+      </c>
+      <c r="D57" t="s">
+        <v>162</v>
+      </c>
+      <c r="E57" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" t="s">
+        <v>12</v>
+      </c>
+      <c r="G57" t="s">
+        <v>163</v>
+      </c>
+      <c r="H57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A58" t="s">
+        <v>164</v>
+      </c>
+      <c r="B58" t="s">
+        <v>129</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" t="s">
+        <v>12</v>
+      </c>
+      <c r="G58" t="s">
+        <v>165</v>
+      </c>
+      <c r="H58" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A59" t="s">
+        <v>166</v>
+      </c>
+      <c r="B59" t="s">
+        <v>38</v>
+      </c>
+      <c r="C59">
+        <v>6</v>
+      </c>
+      <c r="D59" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59" t="s">
+        <v>12</v>
+      </c>
+      <c r="G59" t="s">
+        <v>167</v>
+      </c>
+      <c r="H59" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A60" t="s">
+        <v>168</v>
+      </c>
+      <c r="B60" t="s">
+        <v>147</v>
+      </c>
+      <c r="C60">
+        <v>5</v>
+      </c>
+      <c r="D60" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" t="s">
+        <v>169</v>
+      </c>
+      <c r="H60" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A61" t="s">
+        <v>170</v>
+      </c>
+      <c r="B61" t="s">
+        <v>171</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="D61" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" t="s">
+        <v>12</v>
+      </c>
+      <c r="G61" t="s">
+        <v>172</v>
+      </c>
+      <c r="H61" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A62" t="s">
+        <v>173</v>
+      </c>
+      <c r="B62" t="s">
+        <v>174</v>
+      </c>
+      <c r="C62">
+        <v>14</v>
+      </c>
+      <c r="D62" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" t="s">
+        <v>12</v>
+      </c>
+      <c r="G62" t="s">
+        <v>175</v>
+      </c>
+      <c r="H62" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B63" t="s">
+        <v>174</v>
+      </c>
+      <c r="C63">
+        <v>80</v>
+      </c>
+      <c r="D63" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" t="s">
+        <v>12</v>
+      </c>
+      <c r="G63" t="s">
+        <v>177</v>
+      </c>
+      <c r="H63" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A64" t="s">
+        <v>178</v>
+      </c>
+      <c r="B64" t="s">
+        <v>174</v>
+      </c>
+      <c r="C64">
+        <v>15</v>
+      </c>
+      <c r="D64" t="s">
+        <v>179</v>
+      </c>
+      <c r="E64" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" t="s">
+        <v>12</v>
+      </c>
+      <c r="G64" t="s">
+        <v>180</v>
+      </c>
+      <c r="H64" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A65" t="s">
+        <v>181</v>
+      </c>
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65">
+        <v>20</v>
+      </c>
+      <c r="D65" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" t="s">
+        <v>12</v>
+      </c>
+      <c r="G65" t="s">
+        <v>182</v>
+      </c>
+      <c r="H65" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A66" t="s">
+        <v>183</v>
+      </c>
+      <c r="B66" t="s">
+        <v>184</v>
+      </c>
+      <c r="C66">
+        <v>10</v>
+      </c>
+      <c r="D66" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" t="s">
+        <v>12</v>
+      </c>
+      <c r="G66" t="s">
+        <v>185</v>
+      </c>
+      <c r="H66" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A67" t="s">
+        <v>186</v>
+      </c>
+      <c r="B67" t="s">
+        <v>187</v>
+      </c>
+      <c r="C67">
+        <v>5</v>
+      </c>
+      <c r="D67" t="s">
+        <v>15</v>
+      </c>
+      <c r="E67" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" t="s">
+        <v>12</v>
+      </c>
+      <c r="G67" t="s">
+        <v>188</v>
+      </c>
+      <c r="H67" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A68" t="s">
+        <v>189</v>
+      </c>
+      <c r="B68" t="s">
+        <v>174</v>
+      </c>
+      <c r="C68">
+        <v>8</v>
+      </c>
+      <c r="D68" t="s">
+        <v>15</v>
+      </c>
+      <c r="E68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" t="s">
+        <v>12</v>
+      </c>
+      <c r="G68" t="s">
+        <v>190</v>
+      </c>
+      <c r="H68" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A69" t="s">
+        <v>191</v>
+      </c>
+      <c r="B69" t="s">
+        <v>174</v>
+      </c>
+      <c r="C69">
+        <v>18</v>
+      </c>
+      <c r="D69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E69" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" t="s">
+        <v>12</v>
+      </c>
+      <c r="G69" t="s">
+        <v>192</v>
+      </c>
+      <c r="H69" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A70" t="s">
+        <v>193</v>
+      </c>
+      <c r="B70" t="s">
+        <v>184</v>
+      </c>
+      <c r="C70">
+        <v>30</v>
+      </c>
+      <c r="D70" t="s">
+        <v>15</v>
+      </c>
+      <c r="E70" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" t="s">
+        <v>12</v>
+      </c>
+      <c r="G70" t="s">
+        <v>194</v>
+      </c>
+      <c r="H70" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A71" t="s">
+        <v>195</v>
+      </c>
+      <c r="B71" t="s">
+        <v>187</v>
+      </c>
+      <c r="C71">
+        <v>5</v>
+      </c>
+      <c r="D71" t="s">
+        <v>15</v>
+      </c>
+      <c r="E71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" t="s">
+        <v>12</v>
+      </c>
+      <c r="G71" t="s">
+        <v>196</v>
+      </c>
+      <c r="H71" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A72" t="s">
+        <v>197</v>
+      </c>
+      <c r="B72" t="s">
+        <v>198</v>
+      </c>
+      <c r="C72">
+        <v>20</v>
+      </c>
+      <c r="D72" t="s">
+        <v>15</v>
+      </c>
+      <c r="E72" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" t="s">
+        <v>12</v>
+      </c>
+      <c r="G72" t="s">
+        <v>199</v>
+      </c>
+      <c r="H72" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A73" t="s">
+        <v>200</v>
+      </c>
+      <c r="B73" t="s">
+        <v>187</v>
+      </c>
+      <c r="C73">
+        <v>7</v>
+      </c>
+      <c r="D73" t="s">
+        <v>201</v>
+      </c>
+      <c r="E73" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" t="s">
+        <v>12</v>
+      </c>
+      <c r="G73" t="s">
+        <v>202</v>
+      </c>
+      <c r="H73" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A74" t="s">
+        <v>203</v>
+      </c>
+      <c r="B74" t="s">
+        <v>174</v>
+      </c>
+      <c r="C74">
+        <v>10</v>
+      </c>
+      <c r="D74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" t="s">
+        <v>12</v>
+      </c>
+      <c r="G74" t="s">
+        <v>204</v>
+      </c>
+      <c r="H74" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A75" t="s">
+        <v>205</v>
+      </c>
+      <c r="B75" t="s">
+        <v>184</v>
+      </c>
+      <c r="C75">
+        <v>20</v>
+      </c>
+      <c r="D75" t="s">
+        <v>15</v>
+      </c>
+      <c r="E75" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" t="s">
+        <v>12</v>
+      </c>
+      <c r="G75" t="s">
+        <v>206</v>
+      </c>
+      <c r="H75" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A76" t="s">
+        <v>207</v>
+      </c>
+      <c r="B76" t="s">
+        <v>174</v>
+      </c>
+      <c r="C76">
+        <v>20</v>
+      </c>
+      <c r="D76" t="s">
+        <v>15</v>
+      </c>
+      <c r="E76" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" t="s">
+        <v>12</v>
+      </c>
+      <c r="G76" t="s">
+        <v>208</v>
+      </c>
+      <c r="H76" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A77" t="s">
+        <v>173</v>
+      </c>
+      <c r="B77" t="s">
+        <v>209</v>
+      </c>
+      <c r="C77">
+        <v>5</v>
+      </c>
+      <c r="D77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" t="s">
+        <v>12</v>
+      </c>
+      <c r="G77" t="s">
+        <v>210</v>
+      </c>
+      <c r="H77" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A78" t="s">
+        <v>211</v>
+      </c>
+      <c r="B78" t="s">
+        <v>212</v>
+      </c>
+      <c r="C78">
+        <v>5</v>
+      </c>
+      <c r="D78" t="s">
+        <v>15</v>
+      </c>
+      <c r="E78" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" t="s">
+        <v>12</v>
+      </c>
+      <c r="G78" t="s">
+        <v>213</v>
+      </c>
+      <c r="H78" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A79" t="s">
+        <v>214</v>
+      </c>
+      <c r="B79" t="s">
+        <v>9</v>
+      </c>
+      <c r="C79">
+        <v>4</v>
+      </c>
+      <c r="D79" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" t="s">
+        <v>12</v>
+      </c>
+      <c r="G79" t="s">
+        <v>215</v>
+      </c>
+      <c r="H79" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A80" t="s">
+        <v>216</v>
+      </c>
+      <c r="B80" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80">
+        <v>8</v>
+      </c>
+      <c r="D80" t="s">
+        <v>15</v>
+      </c>
+      <c r="E80" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" t="s">
+        <v>12</v>
+      </c>
+      <c r="G80" t="s">
+        <v>217</v>
+      </c>
+      <c r="H80" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A81" t="s">
+        <v>218</v>
+      </c>
+      <c r="B81" t="s">
+        <v>184</v>
+      </c>
+      <c r="C81">
+        <v>30</v>
+      </c>
+      <c r="D81" t="s">
+        <v>15</v>
+      </c>
+      <c r="E81" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" t="s">
+        <v>12</v>
+      </c>
+      <c r="G81" t="s">
+        <v>219</v>
+      </c>
+      <c r="H81" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A82" t="s">
+        <v>220</v>
+      </c>
+      <c r="B82" t="s">
+        <v>184</v>
+      </c>
+      <c r="C82">
+        <v>10</v>
+      </c>
+      <c r="D82" t="s">
+        <v>15</v>
+      </c>
+      <c r="E82" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" t="s">
+        <v>12</v>
+      </c>
+      <c r="G82" t="s">
+        <v>221</v>
+      </c>
+      <c r="H82" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A83" t="s">
+        <v>222</v>
+      </c>
+      <c r="B83" t="s">
+        <v>187</v>
+      </c>
+      <c r="C83">
+        <v>10</v>
+      </c>
+      <c r="D83" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" t="s">
+        <v>12</v>
+      </c>
+      <c r="G83" t="s">
+        <v>223</v>
+      </c>
+      <c r="H83" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A84" t="s">
+        <v>224</v>
+      </c>
+      <c r="B84" t="s">
+        <v>225</v>
+      </c>
+      <c r="C84">
+        <v>10</v>
+      </c>
+      <c r="D84" t="s">
+        <v>15</v>
+      </c>
+      <c r="E84" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" t="s">
+        <v>12</v>
+      </c>
+      <c r="G84" t="s">
+        <v>226</v>
+      </c>
+      <c r="H84" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A85" t="s">
+        <v>227</v>
+      </c>
+      <c r="B85" t="s">
+        <v>184</v>
+      </c>
+      <c r="C85">
+        <v>20</v>
+      </c>
+      <c r="D85" t="s">
+        <v>15</v>
+      </c>
+      <c r="E85" t="s">
+        <v>12</v>
+      </c>
+      <c r="F85" t="s">
+        <v>12</v>
+      </c>
+      <c r="G85" t="s">
+        <v>228</v>
+      </c>
+      <c r="H85" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A86" t="s">
+        <v>229</v>
+      </c>
+      <c r="B86" t="s">
+        <v>184</v>
+      </c>
+      <c r="C86">
+        <v>25</v>
+      </c>
+      <c r="D86" t="s">
+        <v>15</v>
+      </c>
+      <c r="E86" t="s">
+        <v>12</v>
+      </c>
+      <c r="F86" t="s">
+        <v>12</v>
+      </c>
+      <c r="G86" t="s">
+        <v>230</v>
+      </c>
+      <c r="H86" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A87" t="s">
+        <v>231</v>
+      </c>
+      <c r="B87" t="s">
+        <v>187</v>
+      </c>
+      <c r="C87">
+        <v>20</v>
+      </c>
+      <c r="D87" t="s">
+        <v>15</v>
+      </c>
+      <c r="E87" t="s">
+        <v>12</v>
+      </c>
+      <c r="F87" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" t="s">
+        <v>232</v>
+      </c>
+      <c r="H87" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A88" t="s">
+        <v>233</v>
+      </c>
+      <c r="B88" t="s">
+        <v>187</v>
+      </c>
+      <c r="C88">
+        <v>20</v>
+      </c>
+      <c r="D88" t="s">
+        <v>15</v>
+      </c>
+      <c r="E88" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" t="s">
+        <v>12</v>
+      </c>
+      <c r="G88" t="s">
+        <v>234</v>
+      </c>
+      <c r="H88" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A89" t="s">
+        <v>235</v>
+      </c>
+      <c r="B89" t="s">
+        <v>184</v>
+      </c>
+      <c r="C89">
+        <v>12</v>
+      </c>
+      <c r="D89" t="s">
+        <v>15</v>
+      </c>
+      <c r="E89" t="s">
+        <v>12</v>
+      </c>
+      <c r="F89" t="s">
+        <v>12</v>
+      </c>
+      <c r="G89" t="s">
+        <v>236</v>
+      </c>
+      <c r="H89" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A90" t="s">
+        <v>237</v>
+      </c>
+      <c r="B90" t="s">
+        <v>184</v>
+      </c>
+      <c r="C90">
+        <v>18</v>
+      </c>
+      <c r="D90" t="s">
+        <v>15</v>
+      </c>
+      <c r="E90" t="s">
+        <v>12</v>
+      </c>
+      <c r="F90" t="s">
+        <v>12</v>
+      </c>
+      <c r="G90" t="s">
+        <v>238</v>
+      </c>
+      <c r="H90" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A91" t="s">
+        <v>239</v>
+      </c>
+      <c r="B91" t="s">
+        <v>174</v>
+      </c>
+      <c r="C91">
+        <v>4</v>
+      </c>
+      <c r="D91" t="s">
+        <v>15</v>
+      </c>
+      <c r="E91" t="s">
+        <v>12</v>
+      </c>
+      <c r="F91" t="s">
+        <v>12</v>
+      </c>
+      <c r="G91" t="s">
+        <v>240</v>
+      </c>
+      <c r="H91" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A92" t="s">
+        <v>241</v>
+      </c>
+      <c r="B92" t="s">
+        <v>242</v>
+      </c>
+      <c r="C92">
+        <v>50</v>
+      </c>
+      <c r="D92" t="s">
+        <v>15</v>
+      </c>
+      <c r="E92" t="s">
+        <v>12</v>
+      </c>
+      <c r="F92" t="s">
+        <v>12</v>
+      </c>
+      <c r="G92" t="s">
+        <v>243</v>
+      </c>
+      <c r="H92" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A93" t="s">
+        <v>244</v>
+      </c>
+      <c r="B93" t="s">
+        <v>184</v>
+      </c>
+      <c r="C93">
+        <v>25</v>
+      </c>
+      <c r="D93" t="s">
+        <v>15</v>
+      </c>
+      <c r="E93" t="s">
+        <v>12</v>
+      </c>
+      <c r="F93" t="s">
+        <v>12</v>
+      </c>
+      <c r="G93" t="s">
+        <v>245</v>
+      </c>
+      <c r="H93" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A94" t="s">
+        <v>246</v>
+      </c>
+      <c r="B94" t="s">
+        <v>174</v>
+      </c>
+      <c r="C94">
+        <v>15</v>
+      </c>
+      <c r="D94" t="s">
+        <v>15</v>
+      </c>
+      <c r="E94" t="s">
+        <v>12</v>
+      </c>
+      <c r="F94" t="s">
+        <v>12</v>
+      </c>
+      <c r="G94" t="s">
+        <v>247</v>
+      </c>
+      <c r="H94" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A95" t="s">
+        <v>248</v>
+      </c>
+      <c r="B95" t="s">
+        <v>129</v>
+      </c>
+      <c r="C95">
+        <v>3</v>
+      </c>
+      <c r="D95" t="s">
+        <v>15</v>
+      </c>
+      <c r="E95" t="s">
+        <v>12</v>
+      </c>
+      <c r="F95" t="s">
+        <v>12</v>
+      </c>
+      <c r="G95" t="s">
+        <v>249</v>
+      </c>
+      <c r="H95" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A96" t="s">
+        <v>250</v>
+      </c>
+      <c r="B96" t="s">
+        <v>251</v>
+      </c>
+      <c r="C96">
+        <v>7</v>
+      </c>
+      <c r="D96" t="s">
+        <v>252</v>
+      </c>
+      <c r="E96" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96" t="s">
+        <v>12</v>
+      </c>
+      <c r="G96" t="s">
+        <v>253</v>
+      </c>
+      <c r="H96" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A97" t="s">
+        <v>254</v>
+      </c>
+      <c r="B97" t="s">
+        <v>255</v>
+      </c>
+      <c r="C97">
+        <v>6</v>
+      </c>
+      <c r="D97" t="s">
+        <v>15</v>
+      </c>
+      <c r="E97" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97" t="s">
+        <v>12</v>
+      </c>
+      <c r="G97" t="s">
+        <v>256</v>
+      </c>
+      <c r="H97" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A98" t="s">
+        <v>257</v>
+      </c>
+      <c r="B98" t="s">
+        <v>258</v>
+      </c>
+      <c r="C98">
+        <v>11</v>
+      </c>
+      <c r="D98" t="s">
+        <v>15</v>
+      </c>
+      <c r="E98" t="s">
+        <v>12</v>
+      </c>
+      <c r="F98" t="s">
+        <v>12</v>
+      </c>
+      <c r="G98" t="s">
+        <v>259</v>
+      </c>
+      <c r="H98" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A99" t="s">
+        <v>260</v>
+      </c>
+      <c r="B99" t="s">
+        <v>251</v>
+      </c>
+      <c r="C99">
+        <v>10</v>
+      </c>
+      <c r="D99" t="s">
+        <v>15</v>
+      </c>
+      <c r="E99" t="s">
+        <v>12</v>
+      </c>
+      <c r="F99" t="s">
+        <v>12</v>
+      </c>
+      <c r="G99" t="s">
+        <v>261</v>
+      </c>
+      <c r="H99" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A100" t="s">
+        <v>262</v>
+      </c>
+      <c r="B100" t="s">
+        <v>251</v>
+      </c>
+      <c r="C100">
+        <v>5</v>
+      </c>
+      <c r="D100" t="s">
+        <v>15</v>
+      </c>
+      <c r="E100" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" t="s">
+        <v>263</v>
+      </c>
+      <c r="H100" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A101" t="s">
+        <v>264</v>
+      </c>
+      <c r="B101" t="s">
+        <v>265</v>
+      </c>
+      <c r="C101">
+        <v>12</v>
+      </c>
+      <c r="D101" t="s">
+        <v>15</v>
+      </c>
+      <c r="E101" t="s">
+        <v>12</v>
+      </c>
+      <c r="F101" t="s">
+        <v>12</v>
+      </c>
+      <c r="G101" t="s">
+        <v>266</v>
+      </c>
+      <c r="H101" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A102" t="s">
+        <v>267</v>
+      </c>
+      <c r="B102" t="s">
+        <v>268</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+      <c r="D102" t="s">
+        <v>15</v>
+      </c>
+      <c r="E102" t="s">
+        <v>12</v>
+      </c>
+      <c r="F102" t="s">
+        <v>12</v>
+      </c>
+      <c r="G102" t="s">
+        <v>269</v>
+      </c>
+      <c r="H102" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A103" t="s">
+        <v>270</v>
+      </c>
+      <c r="B103" t="s">
+        <v>271</v>
+      </c>
+      <c r="C103">
+        <v>3</v>
+      </c>
+      <c r="D103" t="s">
+        <v>15</v>
+      </c>
+      <c r="E103" t="s">
+        <v>12</v>
+      </c>
+      <c r="F103" t="s">
+        <v>12</v>
+      </c>
+      <c r="G103" t="s">
+        <v>272</v>
+      </c>
+      <c r="H103" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A104" t="s">
+        <v>273</v>
+      </c>
+      <c r="B104" t="s">
+        <v>255</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="D104" t="s">
+        <v>15</v>
+      </c>
+      <c r="E104" t="s">
+        <v>12</v>
+      </c>
+      <c r="F104" t="s">
+        <v>12</v>
+      </c>
+      <c r="G104" t="s">
+        <v>274</v>
+      </c>
+      <c r="H104" t="s">
+        <v>275</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 A4:G104 A3:G3 A2:B2 D2:G2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>